--- a/output/yearly_total_coral_cover_iteration_98_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_98_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.251665918333509</v>
+        <v>1.282532066155029</v>
       </c>
       <c r="C3" t="n">
-        <v>4.691739771981428</v>
+        <v>4.64493004144294</v>
       </c>
       <c r="D3" t="n">
-        <v>6.06442746891543</v>
+        <v>6.025226283084855</v>
       </c>
       <c r="E3" t="n">
-        <v>12.00783315923037</v>
+        <v>11.95268839068282</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.374325312047207</v>
+        <v>1.449114501115841</v>
       </c>
       <c r="C4" t="n">
-        <v>5.290462693024398</v>
+        <v>5.167401090489362</v>
       </c>
       <c r="D4" t="n">
-        <v>6.284682330098615</v>
+        <v>6.302698514169915</v>
       </c>
       <c r="E4" t="n">
-        <v>12.94947033517022</v>
+        <v>12.91921410577512</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.539535974247288</v>
+        <v>1.667768814454772</v>
       </c>
       <c r="C5" t="n">
-        <v>6.077221223488018</v>
+        <v>5.831680502805584</v>
       </c>
       <c r="D5" t="n">
-        <v>6.546025719513228</v>
+        <v>6.693320820219872</v>
       </c>
       <c r="E5" t="n">
-        <v>14.16278291724853</v>
+        <v>14.19277013748023</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.72961194210621</v>
+        <v>1.902018837106034</v>
       </c>
       <c r="C6" t="n">
-        <v>7.027261091273698</v>
+        <v>6.645257708352842</v>
       </c>
       <c r="D6" t="n">
-        <v>6.933602551018966</v>
+        <v>7.122375999125065</v>
       </c>
       <c r="E6" t="n">
-        <v>15.69047558439887</v>
+        <v>15.66965254458394</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.953649916500031</v>
+        <v>2.153344608961377</v>
       </c>
       <c r="C7" t="n">
-        <v>8.10413705436997</v>
+        <v>7.582508134642124</v>
       </c>
       <c r="D7" t="n">
-        <v>7.227905239674556</v>
+        <v>7.624193376125311</v>
       </c>
       <c r="E7" t="n">
-        <v>17.28569221054456</v>
+        <v>17.36004611972881</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.192784452196941</v>
+        <v>1.317526418793222</v>
       </c>
       <c r="C8" t="n">
-        <v>5.635802459909618</v>
+        <v>5.183128936869046</v>
       </c>
       <c r="D8" t="n">
-        <v>5.509127720354091</v>
+        <v>5.934264435760306</v>
       </c>
       <c r="E8" t="n">
-        <v>12.33771463246065</v>
+        <v>12.43491979142257</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.49889406982498</v>
+        <v>1.633994587995952</v>
       </c>
       <c r="C9" t="n">
-        <v>6.883470017950346</v>
+        <v>6.286704539055684</v>
       </c>
       <c r="D9" t="n">
-        <v>6.062440044546531</v>
+        <v>6.478508838417767</v>
       </c>
       <c r="E9" t="n">
-        <v>14.44480413232186</v>
+        <v>14.3992079654694</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.816431970305914</v>
+        <v>1.969904715030459</v>
       </c>
       <c r="C10" t="n">
-        <v>8.255211744131479</v>
+        <v>7.503983907072994</v>
       </c>
       <c r="D10" t="n">
-        <v>6.66173334045687</v>
+        <v>7.04221609106945</v>
       </c>
       <c r="E10" t="n">
-        <v>16.73337705489426</v>
+        <v>16.5161047131729</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.131816753275463</v>
+        <v>2.323241739945107</v>
       </c>
       <c r="C11" t="n">
-        <v>9.690475613060881</v>
+        <v>8.815344158253847</v>
       </c>
       <c r="D11" t="n">
-        <v>7.189594393491224</v>
+        <v>7.641418141235292</v>
       </c>
       <c r="E11" t="n">
-        <v>19.01188675982757</v>
+        <v>18.78000403943425</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.454858536998952</v>
+        <v>2.691275514945886</v>
       </c>
       <c r="C12" t="n">
-        <v>11.21530567188483</v>
+        <v>10.21990832413743</v>
       </c>
       <c r="D12" t="n">
-        <v>7.76261103235552</v>
+        <v>8.286203001986488</v>
       </c>
       <c r="E12" t="n">
-        <v>21.4327752412393</v>
+        <v>21.19738684106981</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.769977626715473</v>
+        <v>3.063530508431979</v>
       </c>
       <c r="C13" t="n">
-        <v>12.7986004034877</v>
+        <v>11.6906079932836</v>
       </c>
       <c r="D13" t="n">
-        <v>8.384388063188645</v>
+        <v>8.877130316156464</v>
       </c>
       <c r="E13" t="n">
-        <v>23.95296609339182</v>
+        <v>23.63126881787204</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.595722901005723</v>
+        <v>1.785995423565797</v>
       </c>
       <c r="C14" t="n">
-        <v>9.07199674072533</v>
+        <v>8.303916606830796</v>
       </c>
       <c r="D14" t="n">
-        <v>6.417292043579701</v>
+        <v>6.731313864260086</v>
       </c>
       <c r="E14" t="n">
-        <v>17.08501168531075</v>
+        <v>16.82122589465668</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.630810563955504</v>
+        <v>1.853235323829661</v>
       </c>
       <c r="C15" t="n">
-        <v>9.71093778160324</v>
+        <v>8.903872446373065</v>
       </c>
       <c r="D15" t="n">
-        <v>6.489381777502545</v>
+        <v>6.822547678415741</v>
       </c>
       <c r="E15" t="n">
-        <v>17.83113012306129</v>
+        <v>17.57965544861847</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.893428074841526</v>
+        <v>2.164498433461113</v>
       </c>
       <c r="C16" t="n">
-        <v>11.41138371022097</v>
+        <v>10.47145845817507</v>
       </c>
       <c r="D16" t="n">
-        <v>7.029244840067865</v>
+        <v>7.438074036547365</v>
       </c>
       <c r="E16" t="n">
-        <v>20.33405662513036</v>
+        <v>20.07403092818355</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.521060988097753</v>
+        <v>1.744870012234899</v>
       </c>
       <c r="C17" t="n">
-        <v>10.41856189187026</v>
+        <v>9.596760523599336</v>
       </c>
       <c r="D17" t="n">
-        <v>6.576168274557963</v>
+        <v>6.98105084526639</v>
       </c>
       <c r="E17" t="n">
-        <v>18.51579115452597</v>
+        <v>18.32268138110063</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.729260223737375</v>
+        <v>2.000153867770197</v>
       </c>
       <c r="C18" t="n">
-        <v>12.10313296011032</v>
+        <v>11.15112239382514</v>
       </c>
       <c r="D18" t="n">
-        <v>7.05838311192991</v>
+        <v>7.497518860039508</v>
       </c>
       <c r="E18" t="n">
-        <v>20.8907762957776</v>
+        <v>20.64879512163485</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.730742662770787</v>
+        <v>2.015812743652933</v>
       </c>
       <c r="C19" t="n">
-        <v>12.87046696574962</v>
+        <v>11.87035076195635</v>
       </c>
       <c r="D19" t="n">
-        <v>7.187885451597108</v>
+        <v>7.650808946580606</v>
       </c>
       <c r="E19" t="n">
-        <v>21.78909508011752</v>
+        <v>21.53697245218989</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.922968863262313</v>
+        <v>2.257627020685965</v>
       </c>
       <c r="C20" t="n">
-        <v>14.70358627911927</v>
+        <v>13.58841906186531</v>
       </c>
       <c r="D20" t="n">
-        <v>7.717479433176006</v>
+        <v>8.189631356579424</v>
       </c>
       <c r="E20" t="n">
-        <v>24.34403457555759</v>
+        <v>24.0356774391307</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.141144261508322</v>
+        <v>1.347134564813388</v>
       </c>
       <c r="C21" t="n">
-        <v>10.79114496310896</v>
+        <v>9.96456248351836</v>
       </c>
       <c r="D21" t="n">
-        <v>6.493357855704744</v>
+        <v>6.885899857770788</v>
       </c>
       <c r="E21" t="n">
-        <v>18.42564708032203</v>
+        <v>18.19759690610254</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_98_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_98_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.282532066155029</v>
+        <v>1.25246113397395</v>
       </c>
       <c r="C3" t="n">
-        <v>4.64493004144294</v>
+        <v>4.64663828244833</v>
       </c>
       <c r="D3" t="n">
-        <v>6.025226283084855</v>
+        <v>6.052145805135303</v>
       </c>
       <c r="E3" t="n">
-        <v>11.95268839068282</v>
+        <v>11.95124522155758</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.449114501115841</v>
+        <v>1.376111989870997</v>
       </c>
       <c r="C4" t="n">
-        <v>5.167401090489362</v>
+        <v>5.210785820117817</v>
       </c>
       <c r="D4" t="n">
-        <v>6.302698514169915</v>
+        <v>6.279067876110217</v>
       </c>
       <c r="E4" t="n">
-        <v>12.91921410577512</v>
+        <v>12.86596568609903</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.667768814454772</v>
+        <v>1.54717151648767</v>
       </c>
       <c r="C5" t="n">
-        <v>5.831680502805584</v>
+        <v>5.970056999749522</v>
       </c>
       <c r="D5" t="n">
-        <v>6.693320820219872</v>
+        <v>6.545324544857217</v>
       </c>
       <c r="E5" t="n">
-        <v>14.19277013748023</v>
+        <v>14.06255306109441</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.902018837106034</v>
+        <v>1.739360351959437</v>
       </c>
       <c r="C6" t="n">
-        <v>6.645257708352842</v>
+        <v>6.899617059921395</v>
       </c>
       <c r="D6" t="n">
-        <v>7.122375999125065</v>
+        <v>6.822932500476</v>
       </c>
       <c r="E6" t="n">
-        <v>15.66965254458394</v>
+        <v>15.46190991235683</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.153344608961377</v>
+        <v>1.952491413693634</v>
       </c>
       <c r="C7" t="n">
-        <v>7.582508134642124</v>
+        <v>8.005041514283178</v>
       </c>
       <c r="D7" t="n">
-        <v>7.624193376125311</v>
+        <v>7.084308261961593</v>
       </c>
       <c r="E7" t="n">
-        <v>17.36004611972881</v>
+        <v>17.04184118993841</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.317526418793222</v>
+        <v>1.173863508659969</v>
       </c>
       <c r="C8" t="n">
-        <v>5.183128936869046</v>
+        <v>5.673027435214228</v>
       </c>
       <c r="D8" t="n">
-        <v>5.934264435760306</v>
+        <v>5.30703083526804</v>
       </c>
       <c r="E8" t="n">
-        <v>12.43491979142257</v>
+        <v>12.15392177914224</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.633994587995952</v>
+        <v>1.463046072260281</v>
       </c>
       <c r="C9" t="n">
-        <v>6.286704539055684</v>
+        <v>7.027289791873208</v>
       </c>
       <c r="D9" t="n">
-        <v>6.478508838417767</v>
+        <v>5.671436094714168</v>
       </c>
       <c r="E9" t="n">
-        <v>14.3992079654694</v>
+        <v>14.16177195884766</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.969904715030459</v>
+        <v>1.772667360374571</v>
       </c>
       <c r="C10" t="n">
-        <v>7.503983907072994</v>
+        <v>8.56595895690889</v>
       </c>
       <c r="D10" t="n">
-        <v>7.04221609106945</v>
+        <v>6.054197444152038</v>
       </c>
       <c r="E10" t="n">
-        <v>16.5161047131729</v>
+        <v>16.3928237614355</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.323241739945107</v>
+        <v>2.089416729646689</v>
       </c>
       <c r="C11" t="n">
-        <v>8.815344158253847</v>
+        <v>10.26963484379567</v>
       </c>
       <c r="D11" t="n">
-        <v>7.641418141235292</v>
+        <v>6.461620313032816</v>
       </c>
       <c r="E11" t="n">
-        <v>18.78000403943425</v>
+        <v>18.82067188647517</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.691275514945886</v>
+        <v>2.40060596626174</v>
       </c>
       <c r="C12" t="n">
-        <v>10.21990832413743</v>
+        <v>12.02737361033647</v>
       </c>
       <c r="D12" t="n">
-        <v>8.286203001986488</v>
+        <v>6.809959761202355</v>
       </c>
       <c r="E12" t="n">
-        <v>21.19738684106981</v>
+        <v>21.23793933780056</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.063530508431979</v>
+        <v>2.695468318394305</v>
       </c>
       <c r="C13" t="n">
-        <v>11.6906079932836</v>
+        <v>13.90897094275322</v>
       </c>
       <c r="D13" t="n">
-        <v>8.877130316156464</v>
+        <v>7.118018742565558</v>
       </c>
       <c r="E13" t="n">
-        <v>23.63126881787204</v>
+        <v>23.72245800371309</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.785995423565797</v>
+        <v>1.553173955503667</v>
       </c>
       <c r="C14" t="n">
-        <v>8.303916606830796</v>
+        <v>9.776803235081159</v>
       </c>
       <c r="D14" t="n">
-        <v>6.731313864260086</v>
+        <v>5.412384910989709</v>
       </c>
       <c r="E14" t="n">
-        <v>16.82122589465668</v>
+        <v>16.74236210157454</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.853235323829661</v>
+        <v>1.581104677689488</v>
       </c>
       <c r="C15" t="n">
-        <v>8.903872446373065</v>
+        <v>10.68738404824712</v>
       </c>
       <c r="D15" t="n">
-        <v>6.822547678415741</v>
+        <v>5.316497612715922</v>
       </c>
       <c r="E15" t="n">
-        <v>17.57965544861847</v>
+        <v>17.58498633865253</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.164498433461113</v>
+        <v>1.821947024495316</v>
       </c>
       <c r="C16" t="n">
-        <v>10.47145845817507</v>
+        <v>12.71416291375649</v>
       </c>
       <c r="D16" t="n">
-        <v>7.438074036547365</v>
+        <v>5.629753670186995</v>
       </c>
       <c r="E16" t="n">
-        <v>20.07403092818355</v>
+        <v>20.1658636084388</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.744870012234899</v>
+        <v>1.454537763657989</v>
       </c>
       <c r="C17" t="n">
-        <v>9.596760523599336</v>
+        <v>11.74023973871252</v>
       </c>
       <c r="D17" t="n">
-        <v>6.98105084526639</v>
+        <v>5.129396135240565</v>
       </c>
       <c r="E17" t="n">
-        <v>18.32268138110063</v>
+        <v>18.32417363761108</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.000153867770197</v>
+        <v>1.653822730143049</v>
       </c>
       <c r="C18" t="n">
-        <v>11.15112239382514</v>
+        <v>13.80034893878107</v>
       </c>
       <c r="D18" t="n">
-        <v>7.497518860039508</v>
+        <v>5.388940775812294</v>
       </c>
       <c r="E18" t="n">
-        <v>20.64879512163485</v>
+        <v>20.84311244473642</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.015812743652933</v>
+        <v>1.651152376387498</v>
       </c>
       <c r="C19" t="n">
-        <v>11.87035076195635</v>
+        <v>14.85126076879207</v>
       </c>
       <c r="D19" t="n">
-        <v>7.650808946580606</v>
+        <v>5.388930958335252</v>
       </c>
       <c r="E19" t="n">
-        <v>21.53697245218989</v>
+        <v>21.89134410351482</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.257627020685965</v>
+        <v>1.828456011774472</v>
       </c>
       <c r="C20" t="n">
-        <v>13.58841906186531</v>
+        <v>17.04809797163107</v>
       </c>
       <c r="D20" t="n">
-        <v>8.189631356579424</v>
+        <v>5.686115805887805</v>
       </c>
       <c r="E20" t="n">
-        <v>24.0356774391307</v>
+        <v>24.56266978929335</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.347134564813388</v>
+        <v>1.08281863039902</v>
       </c>
       <c r="C21" t="n">
-        <v>9.96456248351836</v>
+        <v>12.48652507357278</v>
       </c>
       <c r="D21" t="n">
-        <v>6.885899857770788</v>
+        <v>4.679382622567912</v>
       </c>
       <c r="E21" t="n">
-        <v>18.19759690610254</v>
+        <v>18.24872632653971</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_98_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_98_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.25246113397395</v>
+        <v>2.586786912849365</v>
       </c>
       <c r="C3" t="n">
-        <v>4.64663828244833</v>
+        <v>7.719322288216496</v>
       </c>
       <c r="D3" t="n">
-        <v>6.052145805135303</v>
+        <v>8.168973189939495</v>
       </c>
       <c r="E3" t="n">
-        <v>11.95124522155758</v>
+        <v>18.47508239100535</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.376111989870997</v>
+        <v>1.056873664128454</v>
       </c>
       <c r="C4" t="n">
-        <v>5.210785820117817</v>
+        <v>4.501709583413361</v>
       </c>
       <c r="D4" t="n">
-        <v>6.279067876110217</v>
+        <v>5.725788405653263</v>
       </c>
       <c r="E4" t="n">
-        <v>12.86596568609903</v>
+        <v>11.28437165319508</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.54717151648767</v>
+        <v>1.138677925832249</v>
       </c>
       <c r="C5" t="n">
-        <v>5.970056999749522</v>
+        <v>5.162763350137245</v>
       </c>
       <c r="D5" t="n">
-        <v>6.545324544857217</v>
+        <v>5.997421975101688</v>
       </c>
       <c r="E5" t="n">
-        <v>14.06255306109441</v>
+        <v>12.29886325107118</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.739360351959437</v>
+        <v>1.23944694433034</v>
       </c>
       <c r="C6" t="n">
-        <v>6.899617059921395</v>
+        <v>5.992777289103408</v>
       </c>
       <c r="D6" t="n">
-        <v>6.822932500476</v>
+        <v>6.295367207475746</v>
       </c>
       <c r="E6" t="n">
-        <v>15.46190991235683</v>
+        <v>13.52759144090949</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.952491413693634</v>
+        <v>1.350416573391705</v>
       </c>
       <c r="C7" t="n">
-        <v>8.005041514283178</v>
+        <v>7.020763220842088</v>
       </c>
       <c r="D7" t="n">
-        <v>7.084308261961593</v>
+        <v>6.650527504621754</v>
       </c>
       <c r="E7" t="n">
-        <v>17.04184118993841</v>
+        <v>15.02170729885555</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.173863508659969</v>
+        <v>1.468667548771152</v>
       </c>
       <c r="C8" t="n">
-        <v>5.673027435214228</v>
+        <v>8.202965943001425</v>
       </c>
       <c r="D8" t="n">
-        <v>5.30703083526804</v>
+        <v>6.974944983458236</v>
       </c>
       <c r="E8" t="n">
-        <v>12.15392177914224</v>
+        <v>16.64657847523081</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.463046072260281</v>
+        <v>1.584857811585995</v>
       </c>
       <c r="C9" t="n">
-        <v>7.027289791873208</v>
+        <v>9.514523354957042</v>
       </c>
       <c r="D9" t="n">
-        <v>5.671436094714168</v>
+        <v>7.335097933828276</v>
       </c>
       <c r="E9" t="n">
-        <v>14.16177195884766</v>
+        <v>18.43447910037131</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.772667360374571</v>
+        <v>0.9993602580609983</v>
       </c>
       <c r="C10" t="n">
-        <v>8.56595895690889</v>
+        <v>7.003081263749687</v>
       </c>
       <c r="D10" t="n">
-        <v>6.054197444152038</v>
+        <v>5.769760710289631</v>
       </c>
       <c r="E10" t="n">
-        <v>16.3928237614355</v>
+        <v>13.77220223210032</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.089416729646689</v>
+        <v>0.9310600702765476</v>
       </c>
       <c r="C11" t="n">
-        <v>10.26963484379567</v>
+        <v>7.47814897783472</v>
       </c>
       <c r="D11" t="n">
-        <v>6.461620313032816</v>
+        <v>5.593762799349307</v>
       </c>
       <c r="E11" t="n">
-        <v>18.82067188647517</v>
+        <v>14.00297184746057</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.40060596626174</v>
+        <v>1.002492033237546</v>
       </c>
       <c r="C12" t="n">
-        <v>12.02737361033647</v>
+        <v>8.8928768720855</v>
       </c>
       <c r="D12" t="n">
-        <v>6.809959761202355</v>
+        <v>6.013675927409752</v>
       </c>
       <c r="E12" t="n">
-        <v>21.23793933780056</v>
+        <v>15.9090448327328</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.695468318394305</v>
+        <v>0.7946265918173684</v>
       </c>
       <c r="C13" t="n">
-        <v>13.90897094275322</v>
+        <v>8.494522923610313</v>
       </c>
       <c r="D13" t="n">
-        <v>7.118018742565558</v>
+        <v>5.488185651234605</v>
       </c>
       <c r="E13" t="n">
-        <v>23.72245800371309</v>
+        <v>14.77733516666229</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.553173955503667</v>
+        <v>0.8577824216315656</v>
       </c>
       <c r="C14" t="n">
-        <v>9.776803235081159</v>
+        <v>9.983166602513839</v>
       </c>
       <c r="D14" t="n">
-        <v>5.412384910989709</v>
+        <v>5.834438249045411</v>
       </c>
       <c r="E14" t="n">
-        <v>16.74236210157454</v>
+        <v>16.67538727319081</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.581104677689488</v>
+        <v>0.8311770588464771</v>
       </c>
       <c r="C15" t="n">
-        <v>10.68738404824712</v>
+        <v>10.82645842803072</v>
       </c>
       <c r="D15" t="n">
-        <v>5.316497612715922</v>
+        <v>5.883977238201705</v>
       </c>
       <c r="E15" t="n">
-        <v>17.58498633865253</v>
+        <v>17.5416127250789</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.821947024495316</v>
+        <v>0.9070465214306707</v>
       </c>
       <c r="C16" t="n">
-        <v>12.71416291375649</v>
+        <v>12.62828944206602</v>
       </c>
       <c r="D16" t="n">
-        <v>5.629753670186995</v>
+        <v>6.273387465091204</v>
       </c>
       <c r="E16" t="n">
-        <v>20.1658636084388</v>
+        <v>19.8087234285879</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.454537763657989</v>
+        <v>0.5469807334211104</v>
       </c>
       <c r="C17" t="n">
-        <v>11.74023973871252</v>
+        <v>9.432042893780807</v>
       </c>
       <c r="D17" t="n">
-        <v>5.129396135240565</v>
+        <v>5.217704341237566</v>
       </c>
       <c r="E17" t="n">
-        <v>18.32417363761108</v>
+        <v>15.19672796843948</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.653822730143049</v>
+        <v>0.4244291674999811</v>
       </c>
       <c r="C18" t="n">
-        <v>13.80034893878107</v>
+        <v>8.355183471946566</v>
       </c>
       <c r="D18" t="n">
-        <v>5.388940775812294</v>
+        <v>4.747663175398278</v>
       </c>
       <c r="E18" t="n">
-        <v>20.84311244473642</v>
+        <v>13.52727581484483</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.651152376387498</v>
+        <v>0.4967937907800135</v>
       </c>
       <c r="C19" t="n">
-        <v>14.85126076879207</v>
+        <v>10.29958388759258</v>
       </c>
       <c r="D19" t="n">
-        <v>5.388930958335252</v>
+        <v>5.211332798637004</v>
       </c>
       <c r="E19" t="n">
-        <v>21.89134410351482</v>
+        <v>16.0077104770096</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.828456011774472</v>
+        <v>0.5620800131124264</v>
       </c>
       <c r="C20" t="n">
-        <v>17.04809797163107</v>
+        <v>12.36295249003923</v>
       </c>
       <c r="D20" t="n">
-        <v>5.686115805887805</v>
+        <v>5.736165303850306</v>
       </c>
       <c r="E20" t="n">
-        <v>24.56266978929335</v>
+        <v>18.66119780700197</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.08281863039902</v>
+        <v>0.6180887196397069</v>
       </c>
       <c r="C21" t="n">
-        <v>12.48652507357278</v>
+        <v>14.4014043357521</v>
       </c>
       <c r="D21" t="n">
-        <v>4.679382622567912</v>
+        <v>6.201248643783148</v>
       </c>
       <c r="E21" t="n">
-        <v>18.24872632653971</v>
+        <v>21.22074169917495</v>
       </c>
     </row>
   </sheetData>
